--- a/public/works/grid/category-intake-checklist-01.xlsx
+++ b/public/works/grid/category-intake-checklist-01.xlsx
@@ -195,7 +195,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -205,12 +205,16 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF282455"/>
       <sz val="14"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="FF2D3142"/>
     </font>
   </fonts>
   <fills count="4">
@@ -227,7 +231,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F5F9"/>
+        <fgColor rgb="FFF0F0F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -241,31 +245,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF868892"/>
       </left>
       <right style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF868892"/>
       </right>
       <top style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF868892"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF868892"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF868892"/>
       </left>
       <right style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF868892"/>
       </right>
       <top style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF868892"/>
       </top>
       <bottom style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF868892"/>
       </bottom>
       <diagonal/>
     </border>
@@ -291,14 +295,14 @@
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
